--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U30_P03S49_EPFD_afterShutdown_vsRelTime.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U30_P03S49_EPFD_afterShutdown_vsRelTime.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="3">
   <si>
     <t>time_offset_from_worst_epfd_slot_s</t>
   </si>
@@ -70,9 +70,9 @@
   <dimension ref="A1:C122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="true"/>
-    <col min="2" max="2" width="12.21875" customWidth="true"/>
-    <col min="3" max="3" width="16.44140625" customWidth="true"/>
+    <col min="1" max="1" width="34.140625" customWidth="true"/>
+    <col min="2" max="2" width="12.42578125" customWidth="true"/>
+    <col min="3" max="3" width="18.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
